--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131771653</v>
+        <v>131771652</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>80395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562655</v>
+        <v>562657</v>
       </c>
       <c r="R4" t="n">
         <v>6908076</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131771652</v>
+        <v>131771653</v>
       </c>
       <c r="B5" t="n">
-        <v>80395</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562657</v>
+        <v>562655</v>
       </c>
       <c r="R5" t="n">
         <v>6908076</v>

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131771643</v>
       </c>
       <c r="B2" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131771647</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131771652</v>
+        <v>131771653</v>
       </c>
       <c r="B4" t="n">
-        <v>80395</v>
+        <v>80329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562657</v>
+        <v>562655</v>
       </c>
       <c r="R4" t="n">
         <v>6908076</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131771653</v>
+        <v>131771652</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>80398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562655</v>
+        <v>562657</v>
       </c>
       <c r="R5" t="n">
         <v>6908076</v>
@@ -1119,7 +1119,7 @@
         <v>131771645</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>131771644</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>131771649</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>131771641</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>131771646</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131771650</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131771648</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>131771654</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -1599,45 +1599,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R10" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,54 +1715,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R11" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131771653</v>
+        <v>131771652</v>
       </c>
       <c r="B4" t="n">
-        <v>80329</v>
+        <v>80398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562655</v>
+        <v>562657</v>
       </c>
       <c r="R4" t="n">
         <v>6908076</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131771652</v>
+        <v>131771653</v>
       </c>
       <c r="B5" t="n">
-        <v>80398</v>
+        <v>80329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562657</v>
+        <v>562655</v>
       </c>
       <c r="R5" t="n">
         <v>6908076</v>
@@ -1599,54 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R10" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,45 +1706,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R11" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131771643</v>
       </c>
       <c r="B2" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131771647</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131771652</v>
       </c>
       <c r="B4" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>131771653</v>
       </c>
       <c r="B5" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>131771645</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>131771644</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>131771649</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>131771641</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,54 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R10" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,45 +1706,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R11" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
         <v>131771648</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>131771654</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131771652</v>
+        <v>131771653</v>
       </c>
       <c r="B4" t="n">
-        <v>80400</v>
+        <v>80331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562657</v>
+        <v>562655</v>
       </c>
       <c r="R4" t="n">
         <v>6908076</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131771653</v>
+        <v>131771652</v>
       </c>
       <c r="B5" t="n">
-        <v>80331</v>
+        <v>80400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562655</v>
+        <v>562657</v>
       </c>
       <c r="R5" t="n">
         <v>6908076</v>

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -1599,45 +1599,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R10" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,54 +1715,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R11" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131771643</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131771652</v>
+        <v>131771653</v>
       </c>
       <c r="B4" t="n">
-        <v>80449</v>
+        <v>80382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562657</v>
+        <v>562655</v>
       </c>
       <c r="R4" t="n">
         <v>6908076</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131771653</v>
+        <v>131771652</v>
       </c>
       <c r="B5" t="n">
-        <v>80380</v>
+        <v>80451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562655</v>
+        <v>562657</v>
       </c>
       <c r="R5" t="n">
         <v>6908076</v>
@@ -1602,7 +1602,7 @@
         <v>131771646</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131771650</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -1599,45 +1599,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R10" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,54 +1715,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R11" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38246-2024 artfynd.xlsx
+++ b/artfynd/A 38246-2024 artfynd.xlsx
@@ -1599,54 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131771650</v>
+        <v>131771646</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562717</v>
+        <v>562740</v>
       </c>
       <c r="R10" t="n">
-        <v>6908025</v>
+        <v>6908085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,45 +1706,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131771646</v>
+        <v>131771650</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562740</v>
+        <v>562717</v>
       </c>
       <c r="R11" t="n">
-        <v>6908085</v>
+        <v>6908025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
